--- a/experiment_summary.xlsx
+++ b/experiment_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Studies\Machine Learning\Projects\imgproc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88620672-AEC1-4002-A5C5-D06E3C1204FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F45A78-6A5F-4E8D-BEFA-5252481365FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25080" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="12">
   <si>
     <t>Method</t>
   </si>
@@ -55,7 +55,7 @@
     <t>F1Score</t>
   </si>
   <si>
-    <t>ConvBlock#</t>
+    <t>ConvLayers</t>
   </si>
 </sst>
 </file>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" customWidth="1"/>
@@ -1435,22 +1435,22 @@
         <v>0.1</v>
       </c>
       <c r="D35">
-        <v>64</v>
+        <v>300</v>
       </c>
       <c r="E35">
         <v>0.9</v>
       </c>
       <c r="F35">
-        <v>69.209999999999994</v>
+        <v>84.75</v>
       </c>
       <c r="G35">
-        <v>70.72</v>
+        <v>84.89</v>
       </c>
       <c r="H35">
-        <v>69.209999999999994</v>
+        <v>84.75</v>
       </c>
       <c r="I35">
-        <v>68.88</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1461,25 +1461,25 @@
         <v>3</v>
       </c>
       <c r="C36">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D36">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="E36">
         <v>0.9</v>
       </c>
       <c r="F36">
-        <v>75.569999999999993</v>
+        <v>83.64</v>
       </c>
       <c r="G36">
-        <v>76.83</v>
+        <v>83.96</v>
       </c>
       <c r="H36">
-        <v>75.569999999999993</v>
+        <v>83.64</v>
       </c>
       <c r="I36">
-        <v>75.14</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1490,25 +1490,25 @@
         <v>3</v>
       </c>
       <c r="C37">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D37">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>0.9</v>
       </c>
       <c r="F37">
-        <v>71.2</v>
+        <v>69.209999999999994</v>
       </c>
       <c r="G37">
-        <v>72.239999999999995</v>
+        <v>70.72</v>
       </c>
       <c r="H37">
-        <v>71.2</v>
+        <v>69.209999999999994</v>
       </c>
       <c r="I37">
-        <v>70.510000000000005</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1522,80 +1522,80 @@
         <v>0.01</v>
       </c>
       <c r="D38">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E38">
         <v>0.9</v>
       </c>
       <c r="F38">
-        <v>79.39</v>
+        <v>75.569999999999993</v>
       </c>
       <c r="G38">
-        <v>79.63</v>
+        <v>76.83</v>
       </c>
       <c r="H38">
-        <v>79.39</v>
+        <v>75.569999999999993</v>
       </c>
       <c r="I38">
-        <v>79.099999999999994</v>
+        <v>75.14</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D39">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F39">
-        <v>29.07</v>
+        <v>71.2</v>
       </c>
       <c r="G39">
-        <v>23.71</v>
+        <v>72.239999999999995</v>
       </c>
       <c r="H39">
-        <v>29.07</v>
+        <v>71.2</v>
       </c>
       <c r="I39">
-        <v>23.05</v>
+        <v>70.510000000000005</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D40">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F40">
-        <v>25.21</v>
+        <v>79.39</v>
       </c>
       <c r="G40">
-        <v>17.309999999999999</v>
+        <v>79.63</v>
       </c>
       <c r="H40">
-        <v>25.21</v>
+        <v>79.39</v>
       </c>
       <c r="I40">
-        <v>16.91</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -1609,22 +1609,22 @@
         <v>0.1</v>
       </c>
       <c r="D41">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>18.82</v>
+        <v>29.07</v>
       </c>
       <c r="G41">
-        <v>9.7100000000000009</v>
+        <v>23.71</v>
       </c>
       <c r="H41">
-        <v>18.82</v>
+        <v>29.07</v>
       </c>
       <c r="I41">
-        <v>9.93</v>
+        <v>23.05</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -1635,25 +1635,25 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D42">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>71.069999999999993</v>
+        <v>25.21</v>
       </c>
       <c r="G42">
-        <v>72.77</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="H42">
-        <v>71.069999999999993</v>
+        <v>25.21</v>
       </c>
       <c r="I42">
-        <v>70.540000000000006</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -1664,25 +1664,25 @@
         <v>4</v>
       </c>
       <c r="C43">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D43">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>78.14</v>
+        <v>18.82</v>
       </c>
       <c r="G43">
-        <v>78.55</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="H43">
-        <v>78.14</v>
+        <v>18.82</v>
       </c>
       <c r="I43">
-        <v>77.81</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -1696,22 +1696,22 @@
         <v>0.01</v>
       </c>
       <c r="D44">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>65.36</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="G44">
-        <v>66.73</v>
+        <v>72.77</v>
       </c>
       <c r="H44">
-        <v>65.36</v>
+        <v>71.069999999999993</v>
       </c>
       <c r="I44">
-        <v>64.430000000000007</v>
+        <v>70.540000000000006</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -1722,25 +1722,25 @@
         <v>4</v>
       </c>
       <c r="C45">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D45">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>86.91</v>
+        <v>78.14</v>
       </c>
       <c r="G45">
-        <v>87.19</v>
+        <v>78.55</v>
       </c>
       <c r="H45">
-        <v>86.91</v>
+        <v>78.14</v>
       </c>
       <c r="I45">
-        <v>86.83</v>
+        <v>77.81</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -1751,25 +1751,25 @@
         <v>4</v>
       </c>
       <c r="C46">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D46">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>88.35</v>
+        <v>65.36</v>
       </c>
       <c r="G46">
-        <v>88.51</v>
+        <v>66.73</v>
       </c>
       <c r="H46">
-        <v>88.35</v>
+        <v>65.36</v>
       </c>
       <c r="I46">
-        <v>88.29</v>
+        <v>64.430000000000007</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -1783,80 +1783,80 @@
         <v>1E-3</v>
       </c>
       <c r="D47">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>84.69</v>
+        <v>86.91</v>
       </c>
       <c r="G47">
-        <v>85.45</v>
+        <v>87.19</v>
       </c>
       <c r="H47">
-        <v>84.69</v>
+        <v>86.91</v>
       </c>
       <c r="I47">
-        <v>84.56</v>
+        <v>86.83</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
       <c r="C48">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
       <c r="D48">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>7.46</v>
+        <v>88.35</v>
       </c>
       <c r="G48">
-        <v>2.35</v>
+        <v>88.51</v>
       </c>
       <c r="H48">
-        <v>7.46</v>
+        <v>88.35</v>
       </c>
       <c r="I48">
-        <v>3.48</v>
+        <v>88.29</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
       <c r="D49">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>73.62</v>
+        <v>84.69</v>
       </c>
       <c r="G49">
-        <v>74.97</v>
+        <v>85.45</v>
       </c>
       <c r="H49">
-        <v>73.62</v>
+        <v>84.69</v>
       </c>
       <c r="I49">
-        <v>73.16</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -1870,22 +1870,22 @@
         <v>0.1</v>
       </c>
       <c r="D50">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>19.190000000000001</v>
+        <v>7.46</v>
       </c>
       <c r="G50">
-        <v>10.96</v>
+        <v>2.35</v>
       </c>
       <c r="H50">
-        <v>19.190000000000001</v>
+        <v>7.46</v>
       </c>
       <c r="I50">
-        <v>11.38</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -1896,25 +1896,25 @@
         <v>4</v>
       </c>
       <c r="C51">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D51">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>61.13</v>
+        <v>73.62</v>
       </c>
       <c r="G51">
-        <v>62.7</v>
+        <v>74.97</v>
       </c>
       <c r="H51">
-        <v>61.13</v>
+        <v>73.62</v>
       </c>
       <c r="I51">
-        <v>59.81</v>
+        <v>73.16</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -1925,25 +1925,25 @@
         <v>4</v>
       </c>
       <c r="C52">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D52">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>77.400000000000006</v>
+        <v>19.190000000000001</v>
       </c>
       <c r="G52">
-        <v>78.19</v>
+        <v>10.96</v>
       </c>
       <c r="H52">
-        <v>77.400000000000006</v>
+        <v>19.190000000000001</v>
       </c>
       <c r="I52">
-        <v>77.02</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -1957,22 +1957,22 @@
         <v>0.01</v>
       </c>
       <c r="D53">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>55.8</v>
+        <v>61.13</v>
       </c>
       <c r="G53">
-        <v>57.66</v>
+        <v>62.7</v>
       </c>
       <c r="H53">
-        <v>55.8</v>
+        <v>61.13</v>
       </c>
       <c r="I53">
-        <v>53.94</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -1983,25 +1983,25 @@
         <v>4</v>
       </c>
       <c r="C54">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D54">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>86.56</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="G54">
-        <v>86.81</v>
+        <v>78.19</v>
       </c>
       <c r="H54">
-        <v>86.56</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="I54">
-        <v>86.42</v>
+        <v>77.02</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2012,25 +2012,25 @@
         <v>4</v>
       </c>
       <c r="C55">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D55">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>88.65</v>
+        <v>55.8</v>
       </c>
       <c r="G55">
-        <v>88.75</v>
+        <v>57.66</v>
       </c>
       <c r="H55">
-        <v>88.65</v>
+        <v>55.8</v>
       </c>
       <c r="I55">
-        <v>88.58</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2044,80 +2044,80 @@
         <v>1E-3</v>
       </c>
       <c r="D56">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>84.79</v>
+        <v>86.56</v>
       </c>
       <c r="G56">
-        <v>85.32</v>
+        <v>86.81</v>
       </c>
       <c r="H56">
-        <v>84.79</v>
+        <v>86.56</v>
       </c>
       <c r="I56">
-        <v>84.7</v>
+        <v>86.42</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
       <c r="D57">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E57">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>85.02</v>
+        <v>88.65</v>
       </c>
       <c r="G57">
-        <v>85.42</v>
+        <v>88.75</v>
       </c>
       <c r="H57">
-        <v>85.02</v>
+        <v>88.65</v>
       </c>
       <c r="I57">
-        <v>84.92</v>
+        <v>88.58</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B58">
         <v>4</v>
       </c>
       <c r="C58">
-        <v>0.1</v>
+        <v>1E-3</v>
       </c>
       <c r="D58">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E58">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>86.92</v>
+        <v>84.79</v>
       </c>
       <c r="G58">
-        <v>87.26</v>
+        <v>85.32</v>
       </c>
       <c r="H58">
-        <v>86.92</v>
+        <v>84.79</v>
       </c>
       <c r="I58">
-        <v>86.79</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2131,22 +2131,22 @@
         <v>0.1</v>
       </c>
       <c r="D59">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E59">
         <v>0.9</v>
       </c>
       <c r="F59">
-        <v>87.04</v>
+        <v>85.02</v>
       </c>
       <c r="G59">
-        <v>87.39</v>
+        <v>85.42</v>
       </c>
       <c r="H59">
-        <v>87.04</v>
+        <v>85.02</v>
       </c>
       <c r="I59">
-        <v>86.89</v>
+        <v>84.92</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2166,16 +2166,16 @@
         <v>0.9</v>
       </c>
       <c r="F60">
-        <v>87.7</v>
+        <v>86.92</v>
       </c>
       <c r="G60">
-        <v>87.84</v>
+        <v>87.26</v>
       </c>
       <c r="H60">
-        <v>87.7</v>
+        <v>86.92</v>
       </c>
       <c r="I60">
-        <v>87.51</v>
+        <v>86.79</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2189,22 +2189,22 @@
         <v>0.1</v>
       </c>
       <c r="D61">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="E61">
         <v>0.9</v>
       </c>
       <c r="F61">
-        <v>72.599999999999994</v>
+        <v>87.04</v>
       </c>
       <c r="G61">
-        <v>73.77</v>
+        <v>87.39</v>
       </c>
       <c r="H61">
-        <v>72.599999999999994</v>
+        <v>87.04</v>
       </c>
       <c r="I61">
-        <v>72.06</v>
+        <v>86.89</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2215,25 +2215,25 @@
         <v>4</v>
       </c>
       <c r="C62">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D62">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E62">
         <v>0.9</v>
       </c>
       <c r="F62">
-        <v>86.53</v>
+        <v>87.7</v>
       </c>
       <c r="G62">
-        <v>87</v>
+        <v>87.84</v>
       </c>
       <c r="H62">
-        <v>86.53</v>
+        <v>87.7</v>
       </c>
       <c r="I62">
-        <v>86.41</v>
+        <v>87.51</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2244,25 +2244,25 @@
         <v>4</v>
       </c>
       <c r="C63">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D63">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E63">
         <v>0.9</v>
       </c>
       <c r="F63">
-        <v>86.96</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="G63">
-        <v>87.06</v>
+        <v>73.77</v>
       </c>
       <c r="H63">
-        <v>86.96</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="I63">
-        <v>86.81</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2276,22 +2276,22 @@
         <v>0.01</v>
       </c>
       <c r="D64">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E64">
         <v>0.9</v>
       </c>
       <c r="F64">
-        <v>86.76</v>
+        <v>86.53</v>
       </c>
       <c r="G64">
-        <v>87.09</v>
+        <v>87</v>
       </c>
       <c r="H64">
-        <v>86.76</v>
+        <v>86.53</v>
       </c>
       <c r="I64">
-        <v>86.58</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2302,25 +2302,25 @@
         <v>4</v>
       </c>
       <c r="C65">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D65">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E65">
         <v>0.9</v>
       </c>
       <c r="F65">
-        <v>77.290000000000006</v>
+        <v>86.96</v>
       </c>
       <c r="G65">
-        <v>77.78</v>
+        <v>87.06</v>
       </c>
       <c r="H65">
-        <v>77.290000000000006</v>
+        <v>86.96</v>
       </c>
       <c r="I65">
-        <v>76.81</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2331,25 +2331,25 @@
         <v>4</v>
       </c>
       <c r="C66">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D66">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E66">
         <v>0.9</v>
       </c>
       <c r="F66">
-        <v>71.33</v>
+        <v>86.76</v>
       </c>
       <c r="G66">
-        <v>72.37</v>
+        <v>87.09</v>
       </c>
       <c r="H66">
-        <v>71.33</v>
+        <v>86.76</v>
       </c>
       <c r="I66">
-        <v>70.48</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -2363,80 +2363,80 @@
         <v>1E-3</v>
       </c>
       <c r="D67">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E67">
         <v>0.9</v>
       </c>
       <c r="F67">
-        <v>80.430000000000007</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="G67">
-        <v>81.040000000000006</v>
+        <v>77.78</v>
       </c>
       <c r="H67">
-        <v>80.430000000000007</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="I67">
-        <v>80.11</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>1E-3</v>
       </c>
       <c r="D68">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F68">
-        <v>88.63</v>
+        <v>71.33</v>
       </c>
       <c r="G68">
-        <v>88.59</v>
+        <v>72.37</v>
       </c>
       <c r="H68">
-        <v>88.63</v>
+        <v>71.33</v>
       </c>
       <c r="I68">
-        <v>88.51</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>1E-3</v>
       </c>
       <c r="D69">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F69">
-        <v>85.26</v>
+        <v>80.430000000000007</v>
       </c>
       <c r="G69">
-        <v>86.16</v>
+        <v>81.040000000000006</v>
       </c>
       <c r="H69">
-        <v>85.26</v>
+        <v>80.430000000000007</v>
       </c>
       <c r="I69">
-        <v>85.27</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2456,16 +2456,16 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="G70">
-        <v>85.79</v>
+        <v>88.59</v>
       </c>
       <c r="H70">
-        <v>85.27</v>
+        <v>88.63</v>
       </c>
       <c r="I70">
-        <v>85.08</v>
+        <v>88.51</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -2485,16 +2485,16 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>87.66</v>
+        <v>85.26</v>
       </c>
       <c r="G71">
-        <v>87.65</v>
+        <v>86.16</v>
       </c>
       <c r="H71">
-        <v>87.66</v>
+        <v>85.26</v>
       </c>
       <c r="I71">
-        <v>87.54</v>
+        <v>85.27</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2508,22 +2508,22 @@
         <v>1E-3</v>
       </c>
       <c r="D72">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>86.89</v>
+        <v>85.27</v>
       </c>
       <c r="G72">
-        <v>86.93</v>
+        <v>85.79</v>
       </c>
       <c r="H72">
-        <v>86.89</v>
+        <v>85.27</v>
       </c>
       <c r="I72">
-        <v>86.72</v>
+        <v>85.08</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -2537,22 +2537,22 @@
         <v>1E-3</v>
       </c>
       <c r="D73">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>87.38</v>
+        <v>87.66</v>
       </c>
       <c r="G73">
-        <v>87.69</v>
+        <v>87.65</v>
       </c>
       <c r="H73">
-        <v>87.38</v>
+        <v>87.66</v>
       </c>
       <c r="I73">
-        <v>87.28</v>
+        <v>87.54</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -2563,7 +2563,7 @@
         <v>5</v>
       </c>
       <c r="C74">
-        <v>2E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="D74">
         <v>256</v>
@@ -2572,16 +2572,16 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>88.96</v>
+        <v>86.89</v>
       </c>
       <c r="G74">
-        <v>88.96</v>
+        <v>86.93</v>
       </c>
       <c r="H74">
-        <v>88.96</v>
+        <v>86.89</v>
       </c>
       <c r="I74">
-        <v>88.84</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -2592,7 +2592,7 @@
         <v>5</v>
       </c>
       <c r="C75">
-        <v>3.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="D75">
         <v>256</v>
@@ -2601,74 +2601,74 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>86.44</v>
+        <v>87.38</v>
       </c>
       <c r="G75">
-        <v>86.64</v>
+        <v>87.69</v>
       </c>
       <c r="H75">
-        <v>86.44</v>
+        <v>87.38</v>
       </c>
       <c r="I75">
-        <v>86.26</v>
+        <v>87.28</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B76">
         <v>5</v>
       </c>
       <c r="C76">
-        <v>0.01</v>
+        <v>2E-3</v>
       </c>
       <c r="D76">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>51.3</v>
+        <v>88.96</v>
       </c>
       <c r="G76">
-        <v>50.93</v>
+        <v>88.96</v>
       </c>
       <c r="H76">
-        <v>51.3</v>
+        <v>88.96</v>
       </c>
       <c r="I76">
-        <v>48.47</v>
+        <v>88.84</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77">
         <v>5</v>
       </c>
       <c r="C77">
-        <v>1E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D77">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>88.44</v>
+        <v>86.44</v>
       </c>
       <c r="G77">
-        <v>88.43</v>
+        <v>86.64</v>
       </c>
       <c r="H77">
-        <v>88.44</v>
+        <v>86.44</v>
       </c>
       <c r="I77">
-        <v>88.33</v>
+        <v>86.26</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -2679,25 +2679,25 @@
         <v>5</v>
       </c>
       <c r="C78">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D78">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>87.09</v>
+        <v>51.3</v>
       </c>
       <c r="G78">
-        <v>87.1</v>
+        <v>50.93</v>
       </c>
       <c r="H78">
-        <v>87.09</v>
+        <v>51.3</v>
       </c>
       <c r="I78">
-        <v>86.93</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -2711,22 +2711,22 @@
         <v>1E-3</v>
       </c>
       <c r="D79">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>86.22</v>
+        <v>88.44</v>
       </c>
       <c r="G79">
-        <v>86.25</v>
+        <v>88.43</v>
       </c>
       <c r="H79">
-        <v>86.22</v>
+        <v>88.44</v>
       </c>
       <c r="I79">
-        <v>86.05</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2737,25 +2737,25 @@
         <v>5</v>
       </c>
       <c r="C80">
-        <v>2E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="D80">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>86.8</v>
+        <v>87.09</v>
       </c>
       <c r="G80">
-        <v>86.81</v>
+        <v>87.1</v>
       </c>
       <c r="H80">
-        <v>86.8</v>
+        <v>87.09</v>
       </c>
       <c r="I80">
-        <v>86.64</v>
+        <v>86.93</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -2766,83 +2766,83 @@
         <v>5</v>
       </c>
       <c r="C81">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="D81">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>68.84</v>
+        <v>86.22</v>
       </c>
       <c r="G81">
-        <v>68.87</v>
+        <v>86.25</v>
       </c>
       <c r="H81">
-        <v>68.84</v>
+        <v>86.22</v>
       </c>
       <c r="I81">
-        <v>67.650000000000006</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B82">
         <v>5</v>
       </c>
       <c r="C82">
-        <v>0.1</v>
+        <v>2E-3</v>
       </c>
       <c r="D82">
         <v>256</v>
       </c>
       <c r="E82">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F82">
-        <v>87.05</v>
+        <v>86.8</v>
       </c>
       <c r="G82">
-        <v>87.07</v>
+        <v>86.81</v>
       </c>
       <c r="H82">
-        <v>87.05</v>
+        <v>86.8</v>
       </c>
       <c r="I82">
-        <v>86.89</v>
+        <v>86.64</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B83">
         <v>5</v>
       </c>
       <c r="C83">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D83">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E83">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>86.59</v>
+        <v>68.84</v>
       </c>
       <c r="G83">
-        <v>86.62</v>
+        <v>68.87</v>
       </c>
       <c r="H83">
-        <v>86.59</v>
+        <v>68.84</v>
       </c>
       <c r="I83">
-        <v>86.43</v>
+        <v>67.650000000000006</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -2853,25 +2853,25 @@
         <v>5</v>
       </c>
       <c r="C84">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D84">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E84">
         <v>0.9</v>
       </c>
       <c r="F84">
-        <v>84.53</v>
+        <v>87.05</v>
       </c>
       <c r="G84">
-        <v>84.62</v>
+        <v>87.07</v>
       </c>
       <c r="H84">
-        <v>84.53</v>
+        <v>87.05</v>
       </c>
       <c r="I84">
-        <v>84.31</v>
+        <v>86.89</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -2885,22 +2885,22 @@
         <v>0.01</v>
       </c>
       <c r="D85">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E85">
         <v>0.9</v>
       </c>
       <c r="F85">
-        <v>80.91</v>
+        <v>86.59</v>
       </c>
       <c r="G85">
-        <v>81.13</v>
+        <v>86.62</v>
       </c>
       <c r="H85">
-        <v>80.91</v>
+        <v>86.59</v>
       </c>
       <c r="I85">
-        <v>80.56</v>
+        <v>86.43</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -2914,22 +2914,22 @@
         <v>0.01</v>
       </c>
       <c r="D86">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E86">
         <v>0.9</v>
       </c>
       <c r="F86">
-        <v>87.17</v>
+        <v>84.53</v>
       </c>
       <c r="G86">
-        <v>87.18</v>
+        <v>84.62</v>
       </c>
       <c r="H86">
-        <v>87.17</v>
+        <v>84.53</v>
       </c>
       <c r="I86">
-        <v>87.01</v>
+        <v>84.31</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -2943,22 +2943,22 @@
         <v>0.01</v>
       </c>
       <c r="D87">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="E87">
         <v>0.9</v>
       </c>
       <c r="F87">
-        <v>86.53</v>
+        <v>80.91</v>
       </c>
       <c r="G87">
-        <v>86.6</v>
+        <v>81.13</v>
       </c>
       <c r="H87">
-        <v>86.53</v>
+        <v>80.91</v>
       </c>
       <c r="I87">
-        <v>86.38</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -2969,7 +2969,7 @@
         <v>5</v>
       </c>
       <c r="C88">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="D88">
         <v>256</v>
@@ -2978,16 +2978,16 @@
         <v>0.9</v>
       </c>
       <c r="F88">
-        <v>88.5</v>
+        <v>87.17</v>
       </c>
       <c r="G88">
-        <v>88.48</v>
+        <v>87.18</v>
       </c>
       <c r="H88">
-        <v>88.5</v>
+        <v>87.17</v>
       </c>
       <c r="I88">
-        <v>88.39</v>
+        <v>87.01</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -2998,25 +2998,25 @@
         <v>5</v>
       </c>
       <c r="C89">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="D89">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E89">
         <v>0.9</v>
       </c>
       <c r="F89">
-        <v>88.71</v>
+        <v>86.53</v>
       </c>
       <c r="G89">
-        <v>88.7</v>
+        <v>86.6</v>
       </c>
       <c r="H89">
-        <v>88.71</v>
+        <v>86.53</v>
       </c>
       <c r="I89">
-        <v>88.6</v>
+        <v>86.38</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -3030,22 +3030,22 @@
         <v>0.2</v>
       </c>
       <c r="D90">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="E90">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>88.8</v>
+        <v>52.88</v>
       </c>
       <c r="G90">
-        <v>88.78</v>
+        <v>54.68</v>
       </c>
       <c r="H90">
-        <v>88.8</v>
+        <v>52.88</v>
       </c>
       <c r="I90">
-        <v>88.68</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -3059,22 +3059,22 @@
         <v>0.2</v>
       </c>
       <c r="D91">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E91">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F91">
-        <v>89.55</v>
+        <v>89.6</v>
       </c>
       <c r="G91">
-        <v>89.52</v>
+        <v>89.59</v>
       </c>
       <c r="H91">
-        <v>89.55</v>
+        <v>89.6</v>
       </c>
       <c r="I91">
-        <v>89.45</v>
+        <v>89.51</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -3088,22 +3088,22 @@
         <v>0.2</v>
       </c>
       <c r="D92">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="E92">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F92">
-        <v>89.86</v>
+        <v>89.6</v>
       </c>
       <c r="G92">
-        <v>89.84</v>
+        <v>89.62</v>
       </c>
       <c r="H92">
-        <v>89.86</v>
+        <v>89.6</v>
       </c>
       <c r="I92">
-        <v>89.78</v>
+        <v>89.52</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3117,22 +3117,22 @@
         <v>0.2</v>
       </c>
       <c r="D93">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="E93">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F93">
-        <v>86.55</v>
+        <v>91.07</v>
       </c>
       <c r="G93">
-        <v>86.74</v>
+        <v>91.07</v>
       </c>
       <c r="H93">
-        <v>86.55</v>
+        <v>91.07</v>
       </c>
       <c r="I93">
-        <v>86.4</v>
+        <v>91.01</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3143,25 +3143,25 @@
         <v>5</v>
       </c>
       <c r="C94">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="D94">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E94">
         <v>0.9</v>
       </c>
       <c r="F94">
-        <v>86.87</v>
+        <v>87.58</v>
       </c>
       <c r="G94">
-        <v>86.86</v>
+        <v>87.55</v>
       </c>
       <c r="H94">
-        <v>86.87</v>
+        <v>87.58</v>
       </c>
       <c r="I94">
-        <v>86.72</v>
+        <v>87.45</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -3172,25 +3172,25 @@
         <v>5</v>
       </c>
       <c r="C95">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D95">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E95">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>88.08</v>
+        <v>87.6</v>
       </c>
       <c r="G95">
-        <v>88.06</v>
+        <v>87.74</v>
       </c>
       <c r="H95">
-        <v>88.08</v>
+        <v>87.6</v>
       </c>
       <c r="I95">
-        <v>87.94</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3201,24 +3201,1097 @@
         <v>5</v>
       </c>
       <c r="C96">
+        <v>0.2</v>
+      </c>
+      <c r="D96">
+        <v>256</v>
+      </c>
+      <c r="E96">
+        <v>0.9</v>
+      </c>
+      <c r="F96">
+        <v>90.55</v>
+      </c>
+      <c r="G96">
+        <v>90.54</v>
+      </c>
+      <c r="H96">
+        <v>90.55</v>
+      </c>
+      <c r="I96">
+        <v>90.48</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1</v>
+      </c>
+      <c r="B97">
+        <v>5</v>
+      </c>
+      <c r="C97">
+        <v>0.2</v>
+      </c>
+      <c r="D97">
+        <v>256</v>
+      </c>
+      <c r="E97">
+        <v>0.9</v>
+      </c>
+      <c r="F97">
+        <v>88.5</v>
+      </c>
+      <c r="G97">
+        <v>88.48</v>
+      </c>
+      <c r="H97">
+        <v>88.5</v>
+      </c>
+      <c r="I97">
+        <v>88.39</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1</v>
+      </c>
+      <c r="B98">
+        <v>5</v>
+      </c>
+      <c r="C98">
+        <v>0.2</v>
+      </c>
+      <c r="D98">
+        <v>256</v>
+      </c>
+      <c r="E98">
+        <v>0.9</v>
+      </c>
+      <c r="F98">
+        <v>88.71</v>
+      </c>
+      <c r="G98">
+        <v>88.7</v>
+      </c>
+      <c r="H98">
+        <v>88.71</v>
+      </c>
+      <c r="I98">
+        <v>88.6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+      <c r="C99">
+        <v>0.2</v>
+      </c>
+      <c r="D99">
+        <v>256</v>
+      </c>
+      <c r="E99">
+        <v>0.9</v>
+      </c>
+      <c r="F99">
+        <v>88.8</v>
+      </c>
+      <c r="G99">
+        <v>88.78</v>
+      </c>
+      <c r="H99">
+        <v>88.8</v>
+      </c>
+      <c r="I99">
+        <v>88.68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1</v>
+      </c>
+      <c r="B100">
+        <v>5</v>
+      </c>
+      <c r="C100">
+        <v>0.2</v>
+      </c>
+      <c r="D100">
+        <v>256</v>
+      </c>
+      <c r="E100">
+        <v>0.9</v>
+      </c>
+      <c r="F100">
+        <v>89.55</v>
+      </c>
+      <c r="G100">
+        <v>89.52</v>
+      </c>
+      <c r="H100">
+        <v>89.55</v>
+      </c>
+      <c r="I100">
+        <v>89.45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101">
+        <v>5</v>
+      </c>
+      <c r="C101">
+        <v>0.2</v>
+      </c>
+      <c r="D101">
+        <v>256</v>
+      </c>
+      <c r="E101">
+        <v>0.9</v>
+      </c>
+      <c r="F101">
+        <v>89.86</v>
+      </c>
+      <c r="G101">
+        <v>89.84</v>
+      </c>
+      <c r="H101">
+        <v>89.86</v>
+      </c>
+      <c r="I101">
+        <v>89.78</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+      <c r="C102">
+        <v>0.2</v>
+      </c>
+      <c r="D102">
+        <v>256</v>
+      </c>
+      <c r="E102">
+        <v>0.9</v>
+      </c>
+      <c r="F102">
+        <v>86.55</v>
+      </c>
+      <c r="G102">
+        <v>86.74</v>
+      </c>
+      <c r="H102">
+        <v>86.55</v>
+      </c>
+      <c r="I102">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103">
+        <v>5</v>
+      </c>
+      <c r="C103">
+        <v>0.2</v>
+      </c>
+      <c r="D103">
+        <v>257</v>
+      </c>
+      <c r="E103">
+        <v>0.9</v>
+      </c>
+      <c r="F103">
+        <v>79.97</v>
+      </c>
+      <c r="G103">
+        <v>80.739999999999995</v>
+      </c>
+      <c r="H103">
+        <v>79.97</v>
+      </c>
+      <c r="I103">
+        <v>79.760000000000005</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104">
+        <v>5</v>
+      </c>
+      <c r="C104">
+        <v>0.2</v>
+      </c>
+      <c r="D104">
+        <v>257</v>
+      </c>
+      <c r="E104">
+        <v>0.9</v>
+      </c>
+      <c r="F104">
+        <v>88.2</v>
+      </c>
+      <c r="G104">
+        <v>88.21</v>
+      </c>
+      <c r="H104">
+        <v>88.2</v>
+      </c>
+      <c r="I104">
+        <v>88.09</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1</v>
+      </c>
+      <c r="B105">
+        <v>5</v>
+      </c>
+      <c r="C105">
+        <v>0.2</v>
+      </c>
+      <c r="D105">
+        <v>259</v>
+      </c>
+      <c r="E105">
+        <v>0.9</v>
+      </c>
+      <c r="F105">
+        <v>89.1</v>
+      </c>
+      <c r="G105">
+        <v>89.29</v>
+      </c>
+      <c r="H105">
+        <v>89.1</v>
+      </c>
+      <c r="I105">
+        <v>89.01</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106">
+        <v>5</v>
+      </c>
+      <c r="C106">
+        <v>0.2</v>
+      </c>
+      <c r="D106">
+        <v>260</v>
+      </c>
+      <c r="E106">
+        <v>0.9</v>
+      </c>
+      <c r="F106">
+        <v>88.67</v>
+      </c>
+      <c r="G106">
+        <v>88.78</v>
+      </c>
+      <c r="H106">
+        <v>88.67</v>
+      </c>
+      <c r="I106">
+        <v>88.62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1</v>
+      </c>
+      <c r="B107">
+        <v>5</v>
+      </c>
+      <c r="C107">
+        <v>0.2</v>
+      </c>
+      <c r="D107">
+        <v>261</v>
+      </c>
+      <c r="E107">
+        <v>0.8</v>
+      </c>
+      <c r="F107">
+        <v>89.64</v>
+      </c>
+      <c r="G107">
+        <v>89.67</v>
+      </c>
+      <c r="H107">
+        <v>89.64</v>
+      </c>
+      <c r="I107">
+        <v>89.57</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108">
+        <v>5</v>
+      </c>
+      <c r="C108">
+        <v>0.2</v>
+      </c>
+      <c r="D108">
+        <v>261</v>
+      </c>
+      <c r="E108">
+        <v>0.9</v>
+      </c>
+      <c r="F108">
+        <v>90.02</v>
+      </c>
+      <c r="G108">
+        <v>90.02</v>
+      </c>
+      <c r="H108">
+        <v>90.02</v>
+      </c>
+      <c r="I108">
+        <v>89.96</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B109">
+        <v>5</v>
+      </c>
+      <c r="C109">
+        <v>0.2</v>
+      </c>
+      <c r="D109">
+        <v>273</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+      <c r="F109">
+        <v>88.95</v>
+      </c>
+      <c r="G109">
+        <v>88.97</v>
+      </c>
+      <c r="H109">
+        <v>88.95</v>
+      </c>
+      <c r="I109">
+        <v>88.87</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1</v>
+      </c>
+      <c r="B110">
+        <v>5</v>
+      </c>
+      <c r="C110">
+        <v>0.2</v>
+      </c>
+      <c r="D110">
+        <v>280</v>
+      </c>
+      <c r="E110">
+        <v>0.9</v>
+      </c>
+      <c r="F110">
+        <v>89.73</v>
+      </c>
+      <c r="G110">
+        <v>89.7</v>
+      </c>
+      <c r="H110">
+        <v>89.73</v>
+      </c>
+      <c r="I110">
+        <v>89.65</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1</v>
+      </c>
+      <c r="B111">
+        <v>5</v>
+      </c>
+      <c r="C111">
+        <v>0.2</v>
+      </c>
+      <c r="D111">
+        <v>284</v>
+      </c>
+      <c r="E111">
+        <v>0.8</v>
+      </c>
+      <c r="F111">
+        <v>89.14</v>
+      </c>
+      <c r="G111">
+        <v>89.22</v>
+      </c>
+      <c r="H111">
+        <v>89.14</v>
+      </c>
+      <c r="I111">
+        <v>89.05</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1</v>
+      </c>
+      <c r="B112">
+        <v>5</v>
+      </c>
+      <c r="C112">
+        <v>0.2</v>
+      </c>
+      <c r="D112">
+        <v>286</v>
+      </c>
+      <c r="E112">
+        <v>0.9</v>
+      </c>
+      <c r="F112">
+        <v>91.59</v>
+      </c>
+      <c r="G112">
+        <v>91.59</v>
+      </c>
+      <c r="H112">
+        <v>91.59</v>
+      </c>
+      <c r="I112">
+        <v>91.53</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1</v>
+      </c>
+      <c r="B113">
+        <v>5</v>
+      </c>
+      <c r="C113">
+        <v>0.2</v>
+      </c>
+      <c r="D113">
+        <v>286</v>
+      </c>
+      <c r="E113">
+        <v>0.9</v>
+      </c>
+      <c r="F113">
+        <v>91.44</v>
+      </c>
+      <c r="G113">
+        <v>91.46</v>
+      </c>
+      <c r="H113">
+        <v>91.44</v>
+      </c>
+      <c r="I113">
+        <v>91.35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114">
+        <v>0.2</v>
+      </c>
+      <c r="D114">
+        <v>286</v>
+      </c>
+      <c r="E114">
+        <v>0.9</v>
+      </c>
+      <c r="F114">
+        <v>91.72</v>
+      </c>
+      <c r="G114">
+        <v>91.69</v>
+      </c>
+      <c r="H114">
+        <v>91.72</v>
+      </c>
+      <c r="I114">
+        <v>91.66</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B115">
+        <v>5</v>
+      </c>
+      <c r="C115">
+        <v>0.2</v>
+      </c>
+      <c r="D115">
+        <v>286</v>
+      </c>
+      <c r="E115">
+        <v>0.9</v>
+      </c>
+      <c r="F115">
+        <v>91.74</v>
+      </c>
+      <c r="G115">
+        <v>91.73</v>
+      </c>
+      <c r="H115">
+        <v>91.74</v>
+      </c>
+      <c r="I115">
+        <v>91.67</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1</v>
+      </c>
+      <c r="B116">
+        <v>5</v>
+      </c>
+      <c r="C116">
+        <v>0.2</v>
+      </c>
+      <c r="D116">
+        <v>286</v>
+      </c>
+      <c r="E116">
+        <v>0.9</v>
+      </c>
+      <c r="F116">
+        <v>91.82</v>
+      </c>
+      <c r="G116">
+        <v>91.83</v>
+      </c>
+      <c r="H116">
+        <v>91.82</v>
+      </c>
+      <c r="I116">
+        <v>91.77</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117">
+        <v>5</v>
+      </c>
+      <c r="C117">
+        <v>0.2</v>
+      </c>
+      <c r="D117">
+        <v>286</v>
+      </c>
+      <c r="E117">
+        <v>0.9</v>
+      </c>
+      <c r="F117">
+        <v>91.93</v>
+      </c>
+      <c r="G117">
+        <v>91.96</v>
+      </c>
+      <c r="H117">
+        <v>91.93</v>
+      </c>
+      <c r="I117">
+        <v>91.89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+      <c r="C118">
+        <v>0.2</v>
+      </c>
+      <c r="D118">
+        <v>290</v>
+      </c>
+      <c r="E118">
+        <v>0.9</v>
+      </c>
+      <c r="F118">
+        <v>88.9</v>
+      </c>
+      <c r="G118">
+        <v>88.97</v>
+      </c>
+      <c r="H118">
+        <v>88.9</v>
+      </c>
+      <c r="I118">
+        <v>88.86</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1</v>
+      </c>
+      <c r="B119">
+        <v>5</v>
+      </c>
+      <c r="C119">
+        <v>0.2</v>
+      </c>
+      <c r="D119">
+        <v>291</v>
+      </c>
+      <c r="E119">
+        <v>0.9</v>
+      </c>
+      <c r="F119">
+        <v>88.18</v>
+      </c>
+      <c r="G119">
+        <v>88.22</v>
+      </c>
+      <c r="H119">
+        <v>88.18</v>
+      </c>
+      <c r="I119">
+        <v>88.12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1</v>
+      </c>
+      <c r="B120">
+        <v>5</v>
+      </c>
+      <c r="C120">
+        <v>0.2</v>
+      </c>
+      <c r="D120">
+        <v>292</v>
+      </c>
+      <c r="E120">
+        <v>0.9</v>
+      </c>
+      <c r="F120">
+        <v>89.85</v>
+      </c>
+      <c r="G120">
+        <v>89.89</v>
+      </c>
+      <c r="H120">
+        <v>89.85</v>
+      </c>
+      <c r="I120">
+        <v>89.78</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+      <c r="C121">
+        <v>0.2</v>
+      </c>
+      <c r="D121">
+        <v>293</v>
+      </c>
+      <c r="E121">
+        <v>0.8</v>
+      </c>
+      <c r="F121">
+        <v>86.64</v>
+      </c>
+      <c r="G121">
+        <v>86.76</v>
+      </c>
+      <c r="H121">
+        <v>86.64</v>
+      </c>
+      <c r="I121">
+        <v>86.53</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1</v>
+      </c>
+      <c r="B122">
+        <v>5</v>
+      </c>
+      <c r="C122">
+        <v>0.2</v>
+      </c>
+      <c r="D122">
+        <v>293</v>
+      </c>
+      <c r="E122">
+        <v>0.8</v>
+      </c>
+      <c r="F122">
+        <v>89.2</v>
+      </c>
+      <c r="G122">
+        <v>89.24</v>
+      </c>
+      <c r="H122">
+        <v>89.2</v>
+      </c>
+      <c r="I122">
+        <v>89.16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123">
+        <v>0.2</v>
+      </c>
+      <c r="D123">
+        <v>293</v>
+      </c>
+      <c r="E123">
+        <v>0.9</v>
+      </c>
+      <c r="F123">
+        <v>64.569999999999993</v>
+      </c>
+      <c r="G123">
+        <v>69.260000000000005</v>
+      </c>
+      <c r="H123">
+        <v>64.569999999999993</v>
+      </c>
+      <c r="I123">
+        <v>64.28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124">
+        <v>5</v>
+      </c>
+      <c r="C124">
+        <v>0.2</v>
+      </c>
+      <c r="D124">
+        <v>302</v>
+      </c>
+      <c r="E124">
+        <v>0.8</v>
+      </c>
+      <c r="F124">
+        <v>91.38</v>
+      </c>
+      <c r="G124">
+        <v>91.39</v>
+      </c>
+      <c r="H124">
+        <v>91.38</v>
+      </c>
+      <c r="I124">
+        <v>91.32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1</v>
+      </c>
+      <c r="B125">
+        <v>5</v>
+      </c>
+      <c r="C125">
+        <v>0.2</v>
+      </c>
+      <c r="D125">
+        <v>312</v>
+      </c>
+      <c r="E125">
+        <v>0.8</v>
+      </c>
+      <c r="F125">
+        <v>88.84</v>
+      </c>
+      <c r="G125">
+        <v>88.93</v>
+      </c>
+      <c r="H125">
+        <v>88.84</v>
+      </c>
+      <c r="I125">
+        <v>88.73</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1</v>
+      </c>
+      <c r="B126">
+        <v>5</v>
+      </c>
+      <c r="C126">
+        <v>0.2</v>
+      </c>
+      <c r="D126">
+        <v>313</v>
+      </c>
+      <c r="E126">
+        <v>0.9</v>
+      </c>
+      <c r="F126">
+        <v>87.82</v>
+      </c>
+      <c r="G126">
+        <v>87.88</v>
+      </c>
+      <c r="H126">
+        <v>87.82</v>
+      </c>
+      <c r="I126">
+        <v>87.75</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1</v>
+      </c>
+      <c r="B127">
+        <v>5</v>
+      </c>
+      <c r="C127">
+        <v>0.2</v>
+      </c>
+      <c r="D127">
+        <v>316</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127">
+        <v>82.81</v>
+      </c>
+      <c r="G127">
+        <v>83.44</v>
+      </c>
+      <c r="H127">
+        <v>82.81</v>
+      </c>
+      <c r="I127">
+        <v>82.63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="C128">
+        <v>0.2</v>
+      </c>
+      <c r="D128">
+        <v>326</v>
+      </c>
+      <c r="E128">
+        <v>0.8</v>
+      </c>
+      <c r="F128">
+        <v>42.16</v>
+      </c>
+      <c r="G128">
+        <v>41.06</v>
+      </c>
+      <c r="H128">
+        <v>42.16</v>
+      </c>
+      <c r="I128">
+        <v>38.47</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1</v>
+      </c>
+      <c r="B129">
+        <v>5</v>
+      </c>
+      <c r="C129">
+        <v>0.2</v>
+      </c>
+      <c r="D129">
+        <v>337</v>
+      </c>
+      <c r="E129">
+        <v>0.9</v>
+      </c>
+      <c r="F129">
+        <v>89.55</v>
+      </c>
+      <c r="G129">
+        <v>89.54</v>
+      </c>
+      <c r="H129">
+        <v>89.55</v>
+      </c>
+      <c r="I129">
+        <v>89.47</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1</v>
+      </c>
+      <c r="B130">
+        <v>5</v>
+      </c>
+      <c r="C130">
+        <v>0.2</v>
+      </c>
+      <c r="D130">
+        <v>347</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>82.14</v>
+      </c>
+      <c r="G130">
+        <v>82.59</v>
+      </c>
+      <c r="H130">
+        <v>82.14</v>
+      </c>
+      <c r="I130">
+        <v>81.83</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1</v>
+      </c>
+      <c r="B131">
+        <v>5</v>
+      </c>
+      <c r="C131">
+        <v>0.02</v>
+      </c>
+      <c r="D131">
+        <v>256</v>
+      </c>
+      <c r="E131">
+        <v>0.9</v>
+      </c>
+      <c r="F131">
+        <v>86.87</v>
+      </c>
+      <c r="G131">
+        <v>86.86</v>
+      </c>
+      <c r="H131">
+        <v>86.87</v>
+      </c>
+      <c r="I131">
+        <v>86.72</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+      <c r="C132">
+        <v>0.3</v>
+      </c>
+      <c r="D132">
+        <v>256</v>
+      </c>
+      <c r="E132">
+        <v>0.9</v>
+      </c>
+      <c r="F132">
+        <v>88.08</v>
+      </c>
+      <c r="G132">
+        <v>88.06</v>
+      </c>
+      <c r="H132">
+        <v>88.08</v>
+      </c>
+      <c r="I132">
+        <v>87.94</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="D96">
+      <c r="D133">
         <v>64</v>
       </c>
-      <c r="E96">
-        <v>0.9</v>
-      </c>
-      <c r="F96">
+      <c r="E133">
+        <v>0.9</v>
+      </c>
+      <c r="F133">
         <v>87.17</v>
       </c>
-      <c r="G96">
+      <c r="G133">
         <v>87.14</v>
       </c>
-      <c r="H96">
+      <c r="H133">
         <v>87.17</v>
       </c>
-      <c r="I96">
+      <c r="I133">
         <v>87.01</v>
       </c>
     </row>
